--- a/finanze.xlsx
+++ b/finanze.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimenti" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arbitraggio" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categorie" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conti" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Movimenti" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arbitraggio" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Categorie" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Conti" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categorie'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conti'!$A$1:$C$3</definedName>
   </definedNames>
@@ -24,8 +24,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="168" formatCode="dd/mm/yyyy hh:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -82,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,6 +101,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -538,8 +548,59 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M_2a07b935e5fc4818b94d3796b60e71f2</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Entrata</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Arbitraggio</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>casalbuttano – soncinese · Pacco 101</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Arbitraggio</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>32 km</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>46295.49591435185</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Conto personale</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>P_7f396000a2784ac99db94c7154efba3b</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -551,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -618,8 +679,56 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P_7f396000a2784ac99db94c7154efba3b</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>casalbuttano</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>soncinese</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>32 km</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Conto personale</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>M_2a07b935e5fc4818b94d3796b60e71f2</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Arbitraggio</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finanze.xlsx
+++ b/finanze.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categorie'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conti'!$A$1:$C$3</definedName>
   </definedNames>
@@ -24,12 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yyyy hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy hh:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -86,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,10 +101,16 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -554,7 +558,7 @@
           <t>M_2a07b935e5fc4818b94d3796b60e71f2</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="8" t="n">
         <v>46271</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -585,7 +589,7 @@
           <t>32 km</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="9" t="n">
         <v>46295.49591435185</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -612,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -625,6 +629,8 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="37" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -678,6 +684,16 @@
           <t>Categoria</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Data incasso</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -685,7 +701,7 @@
           <t>P_7f396000a2784ac99db94c7154efba3b</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="8" t="n">
         <v>46271</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -726,9 +742,11 @@
           <t>Arbitraggio</t>
         </is>
       </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:L2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finanze.xlsx
+++ b/finanze.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Conti" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categorie'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conti'!$A$1:$C$3</definedName>
   </definedNames>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -552,59 +552,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>M_2a07b935e5fc4818b94d3796b60e71f2</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="n">
-        <v>46271</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Entrata</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Arbitraggio</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>casalbuttano – soncinese · Pacco 101</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Arbitraggio</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>32 km</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="n">
-        <v>46295.49591435185</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Conto personale</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>P_7f396000a2784ac99db94c7154efba3b</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -616,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -695,58 +644,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>P_7f396000a2784ac99db94c7154efba3b</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="n">
-        <v>46271</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>casalbuttano</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>soncinese</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>32 km</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Conto personale</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>M_2a07b935e5fc4818b94d3796b60e71f2</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Arbitraggio</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="8" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finanze.xlsx
+++ b/finanze.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categorie'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conti'!$A$1:$C$3</definedName>
   </definedNames>
@@ -24,10 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy hh:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -565,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -644,8 +645,54 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P_c62b259c0d6648699b1f7159e32ac614</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>casalbuttano</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>soncinese</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>32 km</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Arbitraggio</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Da ricevere</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finanze.xlsx
+++ b/finanze.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Conti" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categorie'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conti'!$A$1:$C$3</definedName>
@@ -24,11 +24,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy hh:mm:ss"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -480,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -553,8 +554,59 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M_da96210352154119b49aff6dcf9cc9b0</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Entrata</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Arbitraggio</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>casalbuttano – soncinese · Pacco 101</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Arbitraggio</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>32 km</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>46295.50234953704</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Conto personale</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>P_c62b259c0d6648699b1f7159e32ac614</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -677,8 +729,16 @@
           <t>32 km</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Conto personale</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>M_da96210352154119b49aff6dcf9cc9b0</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Arbitraggio</t>
@@ -686,10 +746,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Da ricevere</t>
-        </is>
-      </c>
-      <c r="L2" s="8" t="n"/>
+          <t>Ricevuto</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>46295</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L2"/>

--- a/finanze.xlsx
+++ b/finanze.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Conti" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categorie'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conti'!$A$1:$C$3</definedName>
@@ -24,12 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy hh:mm:ss"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -481,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -554,59 +553,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>M_da96210352154119b49aff6dcf9cc9b0</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="n">
-        <v>46295</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Entrata</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Arbitraggio</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>casalbuttano – soncinese · Pacco 101</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Arbitraggio</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>32 km</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="n">
-        <v>46295.50234953704</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Conto personale</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>P_c62b259c0d6648699b1f7159e32ac614</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -729,16 +677,8 @@
           <t>32 km</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Conto personale</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>M_da96210352154119b49aff6dcf9cc9b0</t>
-        </is>
-      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Arbitraggio</t>
@@ -746,12 +686,10 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Ricevuto</t>
-        </is>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>46295</v>
-      </c>
+          <t>Da ricevere</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L2"/>

--- a/finanze.xlsx
+++ b/finanze.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movimenti'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Arbitraggio'!$A$1:$N$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categorie'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conti'!$A$1:$C$3</definedName>
   </definedNames>
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy hh:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -112,6 +112,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -581,6 +584,8 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -644,6 +649,16 @@
           <t>Data incasso</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Km</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria partita</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -690,9 +705,11 @@
         </is>
       </c>
       <c r="L2" s="8" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
